--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -36781,6 +36781,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1584">
+      <c r="A1584" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1584" t="n">
+        <v>149089</v>
+      </c>
+      <c r="C1584" t="n">
+        <v>10.1000003814697</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>10.1000003814697</v>
+      </c>
+      <c r="G1584" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -36804,6 +36804,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1585">
+      <c r="A1585" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1585" t="n">
+        <v>88322</v>
+      </c>
+      <c r="C1585" t="n">
+        <v>10.3800001144409</v>
+      </c>
+      <c r="D1585" t="n">
+        <v>9.57999992370605</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>10.0799999237061</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>9.81999969482422</v>
+      </c>
+      <c r="G1585" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -36827,6 +36827,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1586">
+      <c r="A1586" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1586" t="n">
+        <v>39925</v>
+      </c>
+      <c r="C1586" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D1586" t="n">
+        <v>9.64999961853027</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>9.88000011444092</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="G1586" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -36850,6 +36850,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1587">
+      <c r="A1587" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1587" t="n">
+        <v>55026</v>
+      </c>
+      <c r="C1587" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="D1587" t="n">
+        <v>10.039999961853</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>10.039999961853</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>10.2799997329712</v>
+      </c>
+      <c r="G1587" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -36691,22 +36691,22 @@
     </row>
     <row r="1580">
       <c r="A1580" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1580" t="n">
-        <v>48109</v>
+        <v>36368</v>
       </c>
       <c r="C1580" t="n">
-        <v>9.17000007629395</v>
+        <v>9.1899995803833</v>
       </c>
       <c r="D1580" t="n">
-        <v>8.88000011444092</v>
+        <v>8.84000015258789</v>
       </c>
       <c r="E1580" t="n">
-        <v>9.14000034332275</v>
+        <v>9</v>
       </c>
       <c r="F1580" t="n">
-        <v>8.97999954223633</v>
+        <v>9.13000011444092</v>
       </c>
       <c r="G1580" t="s">
         <v>7</v>
@@ -36714,22 +36714,22 @@
     </row>
     <row r="1581">
       <c r="A1581" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1581" t="n">
-        <v>48541</v>
+        <v>48109</v>
       </c>
       <c r="C1581" t="n">
-        <v>9.38000011444092</v>
+        <v>9.17000007629395</v>
       </c>
       <c r="D1581" t="n">
-        <v>9.06999969482422</v>
+        <v>8.88000011444092</v>
       </c>
       <c r="E1581" t="n">
-        <v>9.10000038146973</v>
+        <v>9.14000034332275</v>
       </c>
       <c r="F1581" t="n">
-        <v>9.22999954223633</v>
+        <v>8.97999954223633</v>
       </c>
       <c r="G1581" t="s">
         <v>7</v>
@@ -36737,22 +36737,22 @@
     </row>
     <row r="1582">
       <c r="A1582" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1582" t="n">
-        <v>69907</v>
+        <v>48541</v>
       </c>
       <c r="C1582" t="n">
-        <v>9.35999965667725</v>
+        <v>9.38000011444092</v>
       </c>
       <c r="D1582" t="n">
-        <v>8.82999992370605</v>
+        <v>9.06999969482422</v>
       </c>
       <c r="E1582" t="n">
-        <v>9.25</v>
+        <v>9.10000038146973</v>
       </c>
       <c r="F1582" t="n">
-        <v>8.89999961853027</v>
+        <v>9.22999954223633</v>
       </c>
       <c r="G1582" t="s">
         <v>7</v>
@@ -36760,22 +36760,22 @@
     </row>
     <row r="1583">
       <c r="A1583" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1583" t="n">
-        <v>129840</v>
+        <v>69907</v>
       </c>
       <c r="C1583" t="n">
-        <v>9.75</v>
+        <v>9.35999965667725</v>
       </c>
       <c r="D1583" t="n">
-        <v>9.14999961853027</v>
+        <v>8.82999992370605</v>
       </c>
       <c r="E1583" t="n">
-        <v>9.30000019073486</v>
+        <v>9.25</v>
       </c>
       <c r="F1583" t="n">
-        <v>9.3100004196167</v>
+        <v>8.89999961853027</v>
       </c>
       <c r="G1583" t="s">
         <v>7</v>
@@ -36783,22 +36783,22 @@
     </row>
     <row r="1584">
       <c r="A1584" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1584" t="n">
-        <v>149089</v>
+        <v>129840</v>
       </c>
       <c r="C1584" t="n">
-        <v>10.1000003814697</v>
+        <v>9.75</v>
       </c>
       <c r="D1584" t="n">
-        <v>9.14000034332275</v>
+        <v>9.14999961853027</v>
       </c>
       <c r="E1584" t="n">
-        <v>9.25</v>
+        <v>9.30000019073486</v>
       </c>
       <c r="F1584" t="n">
-        <v>10.1000003814697</v>
+        <v>9.3100004196167</v>
       </c>
       <c r="G1584" t="s">
         <v>7</v>
@@ -36806,22 +36806,22 @@
     </row>
     <row r="1585">
       <c r="A1585" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1585" t="n">
-        <v>88322</v>
+        <v>149089</v>
       </c>
       <c r="C1585" t="n">
-        <v>10.3800001144409</v>
+        <v>10.1000003814697</v>
       </c>
       <c r="D1585" t="n">
-        <v>9.57999992370605</v>
+        <v>9.14000034332275</v>
       </c>
       <c r="E1585" t="n">
-        <v>10.0799999237061</v>
+        <v>9.25</v>
       </c>
       <c r="F1585" t="n">
-        <v>9.81999969482422</v>
+        <v>10.1000003814697</v>
       </c>
       <c r="G1585" t="s">
         <v>7</v>
@@ -36829,22 +36829,22 @@
     </row>
     <row r="1586">
       <c r="A1586" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1586" t="n">
-        <v>39925</v>
+        <v>88322</v>
       </c>
       <c r="C1586" t="n">
-        <v>10.1999998092651</v>
+        <v>10.3800001144409</v>
       </c>
       <c r="D1586" t="n">
-        <v>9.64999961853027</v>
+        <v>9.57999992370605</v>
       </c>
       <c r="E1586" t="n">
-        <v>9.88000011444092</v>
+        <v>10.0799999237061</v>
       </c>
       <c r="F1586" t="n">
-        <v>10.1599998474121</v>
+        <v>9.81999969482422</v>
       </c>
       <c r="G1586" t="s">
         <v>7</v>
@@ -36852,24 +36852,47 @@
     </row>
     <row r="1587">
       <c r="A1587" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1587" t="n">
-        <v>55026</v>
+        <v>39925</v>
       </c>
       <c r="C1587" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D1587" t="n">
+        <v>9.64999961853027</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>9.88000011444092</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="G1587" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1588" t="n">
+        <v>32756</v>
+      </c>
+      <c r="C1588" t="n">
         <v>10.3999996185303</v>
       </c>
-      <c r="D1587" t="n">
-        <v>10.039999961853</v>
-      </c>
-      <c r="E1587" t="n">
-        <v>10.039999961853</v>
-      </c>
-      <c r="F1587" t="n">
-        <v>10.2799997329712</v>
-      </c>
-      <c r="G1587" t="s">
+      <c r="D1588" t="n">
+        <v>10.0799999237061</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>10.1199998855591</v>
+      </c>
+      <c r="G1588" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -41715,6 +41715,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1591">
+      <c r="A1591" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1591" t="n">
+        <v>105081</v>
+      </c>
+      <c r="C1591" t="n">
+        <v>10.5600004196167</v>
+      </c>
+      <c r="D1591" t="n">
+        <v>10.2399997711182</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>10.2799997329712</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="G1591" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="H1591" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -41741,6 +41741,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1592">
+      <c r="A1592" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1592" t="n">
+        <v>132969</v>
+      </c>
+      <c r="C1592" t="n">
+        <v>10.8599996566772</v>
+      </c>
+      <c r="D1592" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="G1592" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="H1592" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -41767,6 +41767,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1593">
+      <c r="A1593" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1593" t="n">
+        <v>28797</v>
+      </c>
+      <c r="C1593" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="D1593" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1593" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1593" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -41793,6 +41793,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1594">
+      <c r="A1594" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1594" t="n">
+        <v>62027</v>
+      </c>
+      <c r="C1594" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="D1594" t="n">
+        <v>9.92000007629395</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>9.97000026702881</v>
+      </c>
+      <c r="G1594" t="n">
+        <v>9.97000026702881</v>
+      </c>
+      <c r="H1594" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -41871,6 +41871,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1597">
+      <c r="A1597" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1597" t="n">
+        <v>134661</v>
+      </c>
+      <c r="C1597" t="n">
+        <v>11.1599998474121</v>
+      </c>
+      <c r="D1597" t="n">
+        <v>10.6599998474121</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>10.9399995803833</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="G1597" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="H1597" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -37165,8 +37165,31 @@
       <c r="E1600" t="n">
         <v>10.8599996566772</v>
       </c>
-      <c r="F1600"/>
+      <c r="F1600" t="n">
+        <v>11.1000003814697</v>
+      </c>
       <c r="G1600" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1601" t="n">
+        <v>165007</v>
+      </c>
+      <c r="C1601" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D1601" t="n">
+        <v>11.2200002670288</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>11.2200002670288</v>
+      </c>
+      <c r="F1601"/>
+      <c r="G1601" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -37188,8 +37188,31 @@
       <c r="E1601" t="n">
         <v>11.2200002670288</v>
       </c>
-      <c r="F1601"/>
+      <c r="F1601" t="n">
+        <v>11.3800001144409</v>
+      </c>
       <c r="G1601" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1602" t="n">
+        <v>92057</v>
+      </c>
+      <c r="C1602" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="D1602" t="n">
+        <v>10.8199996948242</v>
+      </c>
+      <c r="E1602" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="F1602"/>
+      <c r="G1602" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -37211,8 +37211,31 @@
       <c r="E1602" t="n">
         <v>11.3999996185303</v>
       </c>
-      <c r="F1602"/>
+      <c r="F1602" t="n">
+        <v>10.8599996566772</v>
+      </c>
       <c r="G1602" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1603" t="n">
+        <v>169676</v>
+      </c>
+      <c r="C1603" t="n">
+        <v>11.1800003051758</v>
+      </c>
+      <c r="D1603" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="F1603"/>
+      <c r="G1603" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -37234,8 +37234,31 @@
       <c r="E1603" t="n">
         <v>10.6999998092651</v>
       </c>
-      <c r="F1603"/>
+      <c r="F1603" t="n">
+        <v>10.7200002670288</v>
+      </c>
       <c r="G1603" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1604" t="n">
+        <v>87297</v>
+      </c>
+      <c r="C1604" t="n">
+        <v>11.460000038147</v>
+      </c>
+      <c r="D1604" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="F1604"/>
+      <c r="G1604" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -37264,6 +37264,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1605">
+      <c r="A1605" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1605" t="n">
+        <v>121504</v>
+      </c>
+      <c r="C1605" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="D1605" t="n">
+        <v>11.039999961853</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>11.539999961853</v>
+      </c>
+      <c r="F1605" t="n">
+        <v>11.1999998092651</v>
+      </c>
+      <c r="G1605" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -42157,6 +42157,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1608">
+      <c r="A1608" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1608" t="n">
+        <v>56833</v>
+      </c>
+      <c r="C1608" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="D1608" t="n">
+        <v>10.9399995803833</v>
+      </c>
+      <c r="E1608" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>10.960000038147</v>
+      </c>
+      <c r="G1608" t="n">
+        <v>10.960000038147</v>
+      </c>
+      <c r="H1608" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -42183,6 +42183,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1609">
+      <c r="A1609" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1609" t="n">
+        <v>57531</v>
+      </c>
+      <c r="C1609" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="D1609" t="n">
+        <v>10.5799999237061</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>10.9399995803833</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="G1609" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="H1609" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -47068,6 +47068,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1611">
+      <c r="A1611" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1611" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1611" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D1611" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>10.2399997711182</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="G1611" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="H1611" t="n">
+        <v>36158</v>
+      </c>
+      <c r="I1611" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -47097,6 +47097,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1612">
+      <c r="A1612" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1612" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1612" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="D1612" t="n">
+        <v>10.8800001144409</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="G1612" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="H1612" t="n">
+        <v>33478</v>
+      </c>
+      <c r="I1612" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -47126,6 +47126,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1613">
+      <c r="A1613" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1613" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1613" t="n">
+        <v>10.8800001144409</v>
+      </c>
+      <c r="D1613" t="n">
+        <v>10.8800001144409</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>10.4200000762939</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1613" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1613" t="n">
+        <v>30470</v>
+      </c>
+      <c r="I1613" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -47155,6 +47155,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1614">
+      <c r="A1614" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1614" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1614" t="n">
+        <v>10.4399995803833</v>
+      </c>
+      <c r="D1614" t="n">
+        <v>10.5799999237061</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>10.3400001525879</v>
+      </c>
+      <c r="G1614" t="n">
+        <v>10.3400001525879</v>
+      </c>
+      <c r="H1614" t="n">
+        <v>36541</v>
+      </c>
+      <c r="I1614" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -47184,6 +47184,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1615">
+      <c r="A1615" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1615" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1615" t="n">
+        <v>10.7200002670288</v>
+      </c>
+      <c r="D1615" t="n">
+        <v>10.8800001144409</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G1615" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H1615" t="n">
+        <v>39339</v>
+      </c>
+      <c r="I1615" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -47213,6 +47213,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1616">
+      <c r="A1616" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1616" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1616" t="n">
+        <v>10.4799995422363</v>
+      </c>
+      <c r="D1616" t="n">
+        <v>10.8599996566772</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>10.4399995803833</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="G1616" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="H1616" t="n">
+        <v>41542</v>
+      </c>
+      <c r="I1616" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -47242,6 +47242,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1617">
+      <c r="A1617" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1617" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1617" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="D1617" t="n">
+        <v>10.9200000762939</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>10.6199998855591</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="G1617" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="H1617" t="n">
+        <v>31645</v>
+      </c>
+      <c r="I1617" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -47271,6 +47271,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1618">
+      <c r="A1618" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1618" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1618" t="n">
+        <v>10.6800003051758</v>
+      </c>
+      <c r="D1618" t="n">
+        <v>10.9200000762939</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="G1618" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="H1618" t="n">
+        <v>32143</v>
+      </c>
+      <c r="I1618" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CY4.MI.xlsx
+++ b/data/CY4.MI.xlsx
@@ -47300,6 +47300,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1619">
+      <c r="A1619" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1619" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1619" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="D1619" t="n">
+        <v>10.7399997711182</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>10.1199998855591</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="G1619" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="H1619" t="n">
+        <v>86470</v>
+      </c>
+      <c r="I1619" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
